--- a/results/tables/tableA4_emergency_alt_timing.xlsx
+++ b/results/tables/tableA4_emergency_alt_timing.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="84">
+  <si>
+    <t>panel</t>
+  </si>
   <si>
     <t>specification_id</t>
   </si>
@@ -73,40 +76,193 @@
     <t>transformation</t>
   </si>
   <si>
+    <t>A: H4, common development-relevant media exposure (stacked PPML)</t>
+  </si>
+  <si>
+    <t>B: exploratory, crisis-related media -&gt; emergency ODA (former H4 specification, log OLS)</t>
+  </si>
+  <si>
+    <t>H4_primary__nonemergency_contemporaneous</t>
+  </si>
+  <si>
+    <t>H4_primary__emergency_contemporaneous</t>
+  </si>
+  <si>
+    <t>H4_primary__diff_emergency_minus_nonemergency_contemporaneous</t>
+  </si>
+  <si>
+    <t>H4_primary__nonemergency_m1_13</t>
+  </si>
+  <si>
+    <t>H4_primary__emergency_m1_13</t>
+  </si>
+  <si>
+    <t>H4_primary__diff_emergency_minus_nonemergency_m1_13</t>
+  </si>
+  <si>
+    <t>H4_extended__diff_emergency_minus_nonemergency_contemporaneous</t>
+  </si>
+  <si>
+    <t>H4_extended__diff_emergency_minus_nonemergency_m1_13</t>
+  </si>
+  <si>
+    <t>H4_extended__diff_emergency_minus_nonemergency_m14_25</t>
+  </si>
+  <si>
+    <t>H4_extended__diff_emergency_minus_nonemergency_m26_37</t>
+  </si>
+  <si>
+    <t>H4_roll24__diff_emergency_minus_nonemergency_roll24</t>
+  </si>
+  <si>
+    <t>H4_roll36__diff_emergency_minus_nonemergency_roll36</t>
+  </si>
+  <si>
+    <t>H4_roll60__diff_emergency_minus_nonemergency_roll60</t>
+  </si>
+  <si>
+    <t>H4_streak24__diff_emergency_minus_nonemergency_streak_ge24</t>
+  </si>
+  <si>
+    <t>H4_streak36__diff_emergency_minus_nonemergency_streak_ge36</t>
+  </si>
+  <si>
+    <t>H4_streak60__diff_emergency_minus_nonemergency_streak_ge60</t>
+  </si>
+  <si>
+    <t>H4_trim_top1pct__diff_emergency_minus_nonemergency_contemporaneous</t>
+  </si>
+  <si>
     <t>H4_within_emergency_contemporaneous__crisis_media_lag0</t>
   </si>
   <si>
     <t>H4_within_emergency_forward__crisis_media_m1_13</t>
   </si>
   <si>
+    <t>commitment_musd (PPML level)</t>
+  </si>
+  <si>
     <t>ln_emergency_commitment_musd</t>
   </si>
   <si>
+    <t>nonemergency_contemporaneous</t>
+  </si>
+  <si>
+    <t>emergency_contemporaneous</t>
+  </si>
+  <si>
+    <t>diff_emergency_minus_nonemergency_contemporaneous</t>
+  </si>
+  <si>
+    <t>nonemergency_m1_13</t>
+  </si>
+  <si>
+    <t>emergency_m1_13</t>
+  </si>
+  <si>
+    <t>diff_emergency_minus_nonemergency_m1_13</t>
+  </si>
+  <si>
+    <t>diff_emergency_minus_nonemergency_m14_25</t>
+  </si>
+  <si>
+    <t>diff_emergency_minus_nonemergency_m26_37</t>
+  </si>
+  <si>
+    <t>diff_emergency_minus_nonemergency_roll24</t>
+  </si>
+  <si>
+    <t>diff_emergency_minus_nonemergency_roll36</t>
+  </si>
+  <si>
+    <t>diff_emergency_minus_nonemergency_roll60</t>
+  </si>
+  <si>
+    <t>diff_emergency_minus_nonemergency_streak_ge24</t>
+  </si>
+  <si>
+    <t>diff_emergency_minus_nonemergency_streak_ge36</t>
+  </si>
+  <si>
+    <t>diff_emergency_minus_nonemergency_streak_ge60</t>
+  </si>
+  <si>
     <t>crisis_media_lag0</t>
   </si>
   <si>
     <t>crisis_media_m1_13</t>
   </si>
   <si>
+    <t>***</t>
+  </si>
+  <si>
+    <t>+</t>
+  </si>
+  <si>
     <t>**</t>
   </si>
   <si>
+    <t>country x aid_type + year x aid_type</t>
+  </si>
+  <si>
     <t>country + year</t>
   </si>
   <si>
+    <t>country (original, pre-stack)</t>
+  </si>
+  <si>
     <t>country</t>
   </si>
   <si>
+    <t>ln_gdppc;ln_population;log_bilateral_trade;ln_conflict_deaths;ln_disaster_affected (each also interacted with the emergency indicator)</t>
+  </si>
+  <si>
     <t>ln_gdppc;ln_population;log_bilateral_trade;ln_conflict_deaths;ln_disaster_affected</t>
   </si>
   <si>
+    <t>Stacked emergency + non-emergency ODA country-years (common DevRel media exposure), complete cases on media/outcome/controls; PPML drops observations separated by the FE</t>
+  </si>
+  <si>
     <t>Emergency-ODA country-year panel (pooled crisis media -&gt; emergency-reclassified ODA), complete cases on media/outcome/controls</t>
   </si>
   <si>
     <t>contemporaneous (months 0-11 of the commitment year, k=-11..0)</t>
   </si>
   <si>
+    <t>2-13 months pre-allocation</t>
+  </si>
+  <si>
+    <t>14-25 months pre-allocation</t>
+  </si>
+  <si>
+    <t>26-37 months pre-allocation</t>
+  </si>
+  <si>
+    <t>24-month rolling average (months 2-25)</t>
+  </si>
+  <si>
+    <t>36-month rolling average (months 2-37)</t>
+  </si>
+  <si>
+    <t>60-month rolling average (months 2-61)</t>
+  </si>
+  <si>
+    <t>uninterrupted coverage &gt;= 24 months</t>
+  </si>
+  <si>
+    <t>uninterrupted coverage &gt;= 36 months</t>
+  </si>
+  <si>
+    <t>uninterrupted coverage &gt;= 60 months</t>
+  </si>
+  <si>
     <t>2-13 months pre-allocation (forward/pre-allocation-style window)</t>
+  </si>
+  <si>
+    <t>none (PPML log link on level commitments, $M); ln(x+1) media predictors</t>
+  </si>
+  <si>
+    <t>none (PPML log link on level commitments, $M); ln(x+1) media predictors; emergency rows above $12.99M removed</t>
   </si>
   <si>
     <t>ln(x+1)</t>
@@ -467,10 +623,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S3"/>
+  <dimension ref="A1:T20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:20">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -528,114 +684,1093 @@
       <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="2" spans="1:19">
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2">
-        <v>0.0966519096493873</v>
+        <v>41</v>
+      </c>
+      <c r="D2" t="s">
+        <v>43</v>
       </c>
       <c r="E2">
-        <v>0.0368865974240931</v>
+        <v>0.0384045001513007</v>
       </c>
       <c r="F2">
-        <v>0.008855971894480201</v>
-      </c>
-      <c r="G2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H2">
-        <v>0.035978856090469</v>
+        <v>0.0855021921149051</v>
+      </c>
+      <c r="G2">
+        <v>0.6533134095524482</v>
       </c>
       <c r="I2">
-        <v>0.1573249632083057</v>
+        <v>-0.1022340906612025</v>
       </c>
       <c r="J2">
-        <v>0.9</v>
+        <v>0.1790430909638039</v>
       </c>
       <c r="K2">
-        <v>2080</v>
+        <v>0.9</v>
       </c>
       <c r="L2">
+        <v>4122</v>
+      </c>
+      <c r="M2">
         <v>141</v>
       </c>
-      <c r="N2" t="s">
-        <v>25</v>
-      </c>
       <c r="O2" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="P2" t="s">
-        <v>27</v>
+        <v>64</v>
       </c>
       <c r="Q2" t="s">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="R2" t="s">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="S2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19">
+        <v>70</v>
+      </c>
+      <c r="T2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20">
       <c r="A3" t="s">
         <v>20</v>
       </c>
       <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E3">
+        <v>0.7122303642066709</v>
+      </c>
+      <c r="F3">
+        <v>0.1095783057645093</v>
+      </c>
+      <c r="G3">
+        <v>8.045959464351963E-11</v>
+      </c>
+      <c r="H3" t="s">
+        <v>59</v>
+      </c>
+      <c r="I3">
+        <v>0.5319900905347201</v>
+      </c>
+      <c r="J3">
+        <v>0.8924706378786216</v>
+      </c>
+      <c r="K3">
+        <v>0.9</v>
+      </c>
+      <c r="L3">
+        <v>4122</v>
+      </c>
+      <c r="M3">
+        <v>141</v>
+      </c>
+      <c r="O3" t="s">
+        <v>62</v>
+      </c>
+      <c r="P3" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>66</v>
+      </c>
+      <c r="R3" t="s">
+        <v>68</v>
+      </c>
+      <c r="S3" t="s">
+        <v>70</v>
+      </c>
+      <c r="T3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20">
+      <c r="A4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4">
+        <v>0.6738258640553701</v>
+      </c>
+      <c r="F4">
+        <v>0.1406223479559541</v>
+      </c>
+      <c r="G4">
+        <v>1.653402928791792E-06</v>
+      </c>
+      <c r="H4" t="s">
+        <v>59</v>
+      </c>
+      <c r="I4">
+        <v>0.4425226849895871</v>
+      </c>
+      <c r="J4">
+        <v>0.9051290431211532</v>
+      </c>
+      <c r="K4">
+        <v>0.9</v>
+      </c>
+      <c r="L4">
+        <v>4122</v>
+      </c>
+      <c r="M4">
+        <v>141</v>
+      </c>
+      <c r="O4" t="s">
+        <v>62</v>
+      </c>
+      <c r="P4" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>66</v>
+      </c>
+      <c r="R4" t="s">
+        <v>68</v>
+      </c>
+      <c r="S4" t="s">
+        <v>70</v>
+      </c>
+      <c r="T4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20">
+      <c r="A5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5">
+        <v>-0.0307073903514841</v>
+      </c>
+      <c r="F5">
+        <v>0.1528850365371422</v>
+      </c>
+      <c r="G5">
+        <v>0.8408136619268265</v>
+      </c>
+      <c r="I5">
+        <v>-0.2821808972062109</v>
+      </c>
+      <c r="J5">
+        <v>0.2207661165032425</v>
+      </c>
+      <c r="K5">
+        <v>0.9</v>
+      </c>
+      <c r="L5">
+        <v>4122</v>
+      </c>
+      <c r="M5">
+        <v>141</v>
+      </c>
+      <c r="O5" t="s">
+        <v>62</v>
+      </c>
+      <c r="P5" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>66</v>
+      </c>
+      <c r="R5" t="s">
+        <v>68</v>
+      </c>
+      <c r="S5" t="s">
+        <v>71</v>
+      </c>
+      <c r="T5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6">
+        <v>0.1727592146235169</v>
+      </c>
+      <c r="F6">
+        <v>0.091213608053739</v>
+      </c>
+      <c r="G6">
+        <v>0.0582240771381846</v>
+      </c>
+      <c r="H6" t="s">
+        <v>60</v>
+      </c>
+      <c r="I6">
+        <v>0.0227261805889943</v>
+      </c>
+      <c r="J6">
+        <v>0.3227922486580397</v>
+      </c>
+      <c r="K6">
+        <v>0.9</v>
+      </c>
+      <c r="L6">
+        <v>4122</v>
+      </c>
+      <c r="M6">
+        <v>141</v>
+      </c>
+      <c r="O6" t="s">
+        <v>62</v>
+      </c>
+      <c r="P6" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>66</v>
+      </c>
+      <c r="R6" t="s">
+        <v>68</v>
+      </c>
+      <c r="S6" t="s">
+        <v>71</v>
+      </c>
+      <c r="T6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20">
+      <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7">
+        <v>0.2034666049750011</v>
+      </c>
+      <c r="F7">
+        <v>0.1963056250334354</v>
+      </c>
+      <c r="G7">
+        <v>0.2999788573078061</v>
+      </c>
+      <c r="I7">
+        <v>-0.1194274143522208</v>
+      </c>
+      <c r="J7">
+        <v>0.5263606243022232</v>
+      </c>
+      <c r="K7">
+        <v>0.9</v>
+      </c>
+      <c r="L7">
+        <v>4122</v>
+      </c>
+      <c r="M7">
+        <v>141</v>
+      </c>
+      <c r="O7" t="s">
+        <v>62</v>
+      </c>
+      <c r="P7" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>66</v>
+      </c>
+      <c r="R7" t="s">
+        <v>68</v>
+      </c>
+      <c r="S7" t="s">
+        <v>71</v>
+      </c>
+      <c r="T7" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8">
+        <v>0.659666333117827</v>
+      </c>
+      <c r="F8">
+        <v>0.1494705490368564</v>
+      </c>
+      <c r="G8">
+        <v>1.017817192749959E-05</v>
+      </c>
+      <c r="H8" t="s">
+        <v>59</v>
+      </c>
+      <c r="I8">
+        <v>0.4138091584121257</v>
+      </c>
+      <c r="J8">
+        <v>0.9055235078235282</v>
+      </c>
+      <c r="K8">
+        <v>0.9</v>
+      </c>
+      <c r="L8">
+        <v>3803</v>
+      </c>
+      <c r="M8">
+        <v>137</v>
+      </c>
+      <c r="O8" t="s">
+        <v>62</v>
+      </c>
+      <c r="P8" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>66</v>
+      </c>
+      <c r="R8" t="s">
+        <v>68</v>
+      </c>
+      <c r="S8" t="s">
+        <v>70</v>
+      </c>
+      <c r="T8" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" t="s">
+        <v>48</v>
+      </c>
+      <c r="E9">
+        <v>0.3406658257157203</v>
+      </c>
+      <c r="F9">
+        <v>0.2696712931386215</v>
+      </c>
+      <c r="G9">
+        <v>0.2064946000487029</v>
+      </c>
+      <c r="I9">
+        <v>-0.1029039788880349</v>
+      </c>
+      <c r="J9">
+        <v>0.7842356303194755</v>
+      </c>
+      <c r="K9">
+        <v>0.9</v>
+      </c>
+      <c r="L9">
+        <v>3803</v>
+      </c>
+      <c r="M9">
+        <v>137</v>
+      </c>
+      <c r="O9" t="s">
+        <v>62</v>
+      </c>
+      <c r="P9" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>66</v>
+      </c>
+      <c r="R9" t="s">
+        <v>68</v>
+      </c>
+      <c r="S9" t="s">
+        <v>71</v>
+      </c>
+      <c r="T9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20">
+      <c r="A10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" t="s">
+        <v>49</v>
+      </c>
+      <c r="E10">
+        <v>-0.3399538245505653</v>
+      </c>
+      <c r="F10">
+        <v>0.3118120660087213</v>
+      </c>
+      <c r="G10">
+        <v>0.2756020173956011</v>
+      </c>
+      <c r="I10">
+        <v>-0.8528390322522426</v>
+      </c>
+      <c r="J10">
+        <v>0.1729313831511119</v>
+      </c>
+      <c r="K10">
+        <v>0.9</v>
+      </c>
+      <c r="L10">
+        <v>3803</v>
+      </c>
+      <c r="M10">
+        <v>137</v>
+      </c>
+      <c r="O10" t="s">
+        <v>62</v>
+      </c>
+      <c r="P10" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>66</v>
+      </c>
+      <c r="R10" t="s">
+        <v>68</v>
+      </c>
+      <c r="S10" t="s">
+        <v>72</v>
+      </c>
+      <c r="T10" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" t="s">
+        <v>50</v>
+      </c>
+      <c r="E11">
+        <v>-0.1201066799539794</v>
+      </c>
+      <c r="F11">
+        <v>0.1223319930416318</v>
+      </c>
+      <c r="G11">
+        <v>0.3261938398847144</v>
+      </c>
+      <c r="I11">
+        <v>-0.3213249024007097</v>
+      </c>
+      <c r="J11">
+        <v>0.0811115424927509</v>
+      </c>
+      <c r="K11">
+        <v>0.9</v>
+      </c>
+      <c r="L11">
+        <v>3803</v>
+      </c>
+      <c r="M11">
+        <v>137</v>
+      </c>
+      <c r="O11" t="s">
+        <v>62</v>
+      </c>
+      <c r="P11" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>66</v>
+      </c>
+      <c r="R11" t="s">
+        <v>68</v>
+      </c>
+      <c r="S11" t="s">
+        <v>73</v>
+      </c>
+      <c r="T11" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20">
+      <c r="A12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" t="s">
+        <v>51</v>
+      </c>
+      <c r="E12">
+        <v>-0.0366747329979375</v>
+      </c>
+      <c r="F12">
+        <v>0.372129946086227</v>
+      </c>
+      <c r="G12">
+        <v>0.92149273985668</v>
+      </c>
+      <c r="I12">
+        <v>-0.6487740245151239</v>
+      </c>
+      <c r="J12">
+        <v>0.5754245585192488</v>
+      </c>
+      <c r="K12">
+        <v>0.9</v>
+      </c>
+      <c r="L12">
+        <v>4122</v>
+      </c>
+      <c r="M12">
+        <v>141</v>
+      </c>
+      <c r="O12" t="s">
+        <v>62</v>
+      </c>
+      <c r="P12" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>66</v>
+      </c>
+      <c r="R12" t="s">
+        <v>68</v>
+      </c>
+      <c r="S12" t="s">
+        <v>74</v>
+      </c>
+      <c r="T12" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20">
+      <c r="A13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" t="s">
+        <v>52</v>
+      </c>
+      <c r="E13">
+        <v>-0.1583756234158663</v>
+      </c>
+      <c r="F13">
+        <v>0.3987162192481401</v>
+      </c>
+      <c r="G13">
+        <v>0.6912097347756223</v>
+      </c>
+      <c r="I13">
+        <v>-0.8142054427705481</v>
+      </c>
+      <c r="J13">
+        <v>0.4974541959388154</v>
+      </c>
+      <c r="K13">
+        <v>0.9</v>
+      </c>
+      <c r="L13">
+        <v>3803</v>
+      </c>
+      <c r="M13">
+        <v>137</v>
+      </c>
+      <c r="O13" t="s">
+        <v>62</v>
+      </c>
+      <c r="P13" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>66</v>
+      </c>
+      <c r="R13" t="s">
+        <v>68</v>
+      </c>
+      <c r="S13" t="s">
+        <v>75</v>
+      </c>
+      <c r="T13" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20">
+      <c r="A14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" t="s">
+        <v>53</v>
+      </c>
+      <c r="E14">
+        <v>-0.1855441020054217</v>
+      </c>
+      <c r="F14">
+        <v>0.4984625145568514</v>
+      </c>
+      <c r="G14">
+        <v>0.7097195202714066</v>
+      </c>
+      <c r="I14">
+        <v>-1.00544197697361</v>
+      </c>
+      <c r="J14">
+        <v>0.6343537729627664</v>
+      </c>
+      <c r="K14">
+        <v>0.9</v>
+      </c>
+      <c r="L14">
+        <v>3256</v>
+      </c>
+      <c r="M14">
+        <v>137</v>
+      </c>
+      <c r="O14" t="s">
+        <v>62</v>
+      </c>
+      <c r="P14" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>66</v>
+      </c>
+      <c r="R14" t="s">
+        <v>68</v>
+      </c>
+      <c r="S14" t="s">
+        <v>76</v>
+      </c>
+      <c r="T14" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20">
+      <c r="A15" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15" t="s">
+        <v>54</v>
+      </c>
+      <c r="E15">
+        <v>-0.4279517071197655</v>
+      </c>
+      <c r="F15">
+        <v>0.3475633068693263</v>
+      </c>
+      <c r="G15">
+        <v>0.2182139010734394</v>
+      </c>
+      <c r="I15">
+        <v>-0.9996424730190244</v>
+      </c>
+      <c r="J15">
+        <v>0.1437390587794934</v>
+      </c>
+      <c r="K15">
+        <v>0.9</v>
+      </c>
+      <c r="L15">
+        <v>4122</v>
+      </c>
+      <c r="M15">
+        <v>141</v>
+      </c>
+      <c r="O15" t="s">
+        <v>62</v>
+      </c>
+      <c r="P15" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>66</v>
+      </c>
+      <c r="R15" t="s">
+        <v>68</v>
+      </c>
+      <c r="S15" t="s">
+        <v>77</v>
+      </c>
+      <c r="T15" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20">
+      <c r="A16" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" t="s">
+        <v>41</v>
+      </c>
+      <c r="D16" t="s">
+        <v>55</v>
+      </c>
+      <c r="E16">
+        <v>-0.4956669516925321</v>
+      </c>
+      <c r="F16">
+        <v>0.4021172923790161</v>
+      </c>
+      <c r="G16">
+        <v>0.2177090923436413</v>
+      </c>
+      <c r="I16">
+        <v>-1.157091038522062</v>
+      </c>
+      <c r="J16">
+        <v>0.1657571351369982</v>
+      </c>
+      <c r="K16">
+        <v>0.9</v>
+      </c>
+      <c r="L16">
+        <v>4122</v>
+      </c>
+      <c r="M16">
+        <v>141</v>
+      </c>
+      <c r="O16" t="s">
+        <v>62</v>
+      </c>
+      <c r="P16" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>66</v>
+      </c>
+      <c r="R16" t="s">
+        <v>68</v>
+      </c>
+      <c r="S16" t="s">
+        <v>78</v>
+      </c>
+      <c r="T16" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20">
+      <c r="A17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" t="s">
+        <v>41</v>
+      </c>
+      <c r="D17" t="s">
+        <v>56</v>
+      </c>
+      <c r="E17">
+        <v>0.6628023111981703</v>
+      </c>
+      <c r="F17">
+        <v>0.3500087470018668</v>
+      </c>
+      <c r="G17">
+        <v>0.0582683524340725</v>
+      </c>
+      <c r="H17" t="s">
+        <v>60</v>
+      </c>
+      <c r="I17">
+        <v>0.0870891542274094</v>
+      </c>
+      <c r="J17">
+        <v>1.238515468168931</v>
+      </c>
+      <c r="K17">
+        <v>0.9</v>
+      </c>
+      <c r="L17">
+        <v>4122</v>
+      </c>
+      <c r="M17">
+        <v>141</v>
+      </c>
+      <c r="O17" t="s">
+        <v>62</v>
+      </c>
+      <c r="P17" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>66</v>
+      </c>
+      <c r="R17" t="s">
+        <v>68</v>
+      </c>
+      <c r="S17" t="s">
+        <v>79</v>
+      </c>
+      <c r="T17" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20">
+      <c r="A18" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" t="s">
+        <v>41</v>
+      </c>
+      <c r="D18" t="s">
+        <v>45</v>
+      </c>
+      <c r="E18">
+        <v>0.5234017459953458</v>
+      </c>
+      <c r="F18">
+        <v>0.1933950308186833</v>
+      </c>
+      <c r="G18">
+        <v>0.0068019781349719</v>
+      </c>
+      <c r="H18" t="s">
+        <v>61</v>
+      </c>
+      <c r="I18">
+        <v>0.2052952281188428</v>
+      </c>
+      <c r="J18">
+        <v>0.8415082638718488</v>
+      </c>
+      <c r="K18">
+        <v>0.9</v>
+      </c>
+      <c r="L18">
+        <v>4099</v>
+      </c>
+      <c r="M18">
+        <v>141</v>
+      </c>
+      <c r="O18" t="s">
+        <v>62</v>
+      </c>
+      <c r="P18" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>66</v>
+      </c>
+      <c r="R18" t="s">
+        <v>68</v>
+      </c>
+      <c r="S18" t="s">
+        <v>70</v>
+      </c>
+      <c r="T18" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20">
+      <c r="A19" t="s">
         <v>21</v>
       </c>
-      <c r="C3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3">
+      <c r="B19" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" t="s">
+        <v>42</v>
+      </c>
+      <c r="D19" t="s">
+        <v>57</v>
+      </c>
+      <c r="E19">
+        <v>0.0966519096493873</v>
+      </c>
+      <c r="F19">
+        <v>0.0368865974240931</v>
+      </c>
+      <c r="G19">
+        <v>0.008855971894480201</v>
+      </c>
+      <c r="H19" t="s">
+        <v>61</v>
+      </c>
+      <c r="I19">
+        <v>0.035978856090469</v>
+      </c>
+      <c r="J19">
+        <v>0.1573249632083057</v>
+      </c>
+      <c r="K19">
+        <v>0.9</v>
+      </c>
+      <c r="L19">
+        <v>2080</v>
+      </c>
+      <c r="M19">
+        <v>141</v>
+      </c>
+      <c r="O19" t="s">
+        <v>63</v>
+      </c>
+      <c r="P19" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>67</v>
+      </c>
+      <c r="R19" t="s">
+        <v>69</v>
+      </c>
+      <c r="S19" t="s">
+        <v>70</v>
+      </c>
+      <c r="T19" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20">
+      <c r="A20" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" t="s">
+        <v>42</v>
+      </c>
+      <c r="D20" t="s">
+        <v>58</v>
+      </c>
+      <c r="E20">
         <v>0.0405039334663114</v>
       </c>
-      <c r="E3">
+      <c r="F20">
         <v>0.027748013618049</v>
       </c>
-      <c r="F3">
+      <c r="G20">
         <v>0.1445240444231859</v>
       </c>
-      <c r="H3">
+      <c r="I20">
         <v>-0.0051374873740353</v>
       </c>
-      <c r="I3">
+      <c r="J20">
         <v>0.08614535430665821</v>
       </c>
-      <c r="J3">
-        <v>0.9</v>
-      </c>
-      <c r="K3">
+      <c r="K20">
+        <v>0.9</v>
+      </c>
+      <c r="L20">
         <v>2214</v>
       </c>
-      <c r="L3">
+      <c r="M20">
         <v>141</v>
       </c>
-      <c r="N3" t="s">
-        <v>25</v>
-      </c>
-      <c r="O3" t="s">
-        <v>26</v>
-      </c>
-      <c r="P3" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>28</v>
-      </c>
-      <c r="R3" t="s">
-        <v>30</v>
-      </c>
-      <c r="S3" t="s">
-        <v>31</v>
+      <c r="O20" t="s">
+        <v>63</v>
+      </c>
+      <c r="P20" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>67</v>
+      </c>
+      <c r="R20" t="s">
+        <v>69</v>
+      </c>
+      <c r="S20" t="s">
+        <v>80</v>
+      </c>
+      <c r="T20" t="s">
+        <v>83</v>
       </c>
     </row>
   </sheetData>

--- a/results/tables/tableA4_emergency_alt_timing.xlsx
+++ b/results/tables/tableA4_emergency_alt_timing.xlsx
@@ -175,16 +175,16 @@
     <t>country x aid_type + year x aid_type</t>
   </si>
   <si>
-    <t>country (original, pre-stack)</t>
+    <t>country</t>
   </si>
   <si>
     <t>ln_gdppc;ln_population;log_bilateral_trade;ln_conflict_deaths;ln_disaster_affected (each also interacted with the emergency indicator)</t>
   </si>
   <si>
-    <t>Stacked emergency + non-emergency ODA country-years (common DevRel media exposure), complete cases on media/outcome/controls; PPML drops observations separated by the FE</t>
-  </si>
-  <si>
-    <t>contemporaneous (months 0-11 of the commitment year, k=-11..0)</t>
+    <t>Stacked emergency and non-emergency ODA country-years, complete cases; PPML drops observations separated by the fixed effects</t>
+  </si>
+  <si>
+    <t>contemporaneous (months 0-11 of the commitment year)</t>
   </si>
   <si>
     <t>2-13 months pre-allocation</t>
@@ -214,15 +214,23 @@
     <t>uninterrupted coverage &gt;= 60 months</t>
   </si>
   <si>
-    <t>none (PPML log link on level commitments, $M); ln(x+1) media predictors</t>
+    <t>PPML (log link, commitments in $M); ln(x+1) media</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -238,7 +246,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -246,12 +254,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -550,61 +576,61 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:19">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
     </row>
